--- a/graficos/BERT_mejores_umass.xlsx
+++ b/graficos/BERT_mejores_umass.xlsx
@@ -79,46 +79,46 @@
     <t>orps_dictamen_K5_0.05</t>
   </si>
   <si>
-    <t>denuncia_dictamen</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dictamen_K6_0.05</t>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dictamen_K6_0.05</t>
   </si>
   <si>
     <t>todos</t>
   </si>
   <si>
-    <t>todos_denuncia_dictamen_K6_0.05</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen_bert</t>
-  </si>
-  <si>
-    <t>orps_denuncia_dictamen_bert_K6_0.05</t>
-  </si>
-  <si>
-    <t>todos_denuncia_dictamen_bert_K5_0.05</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_K7_0.05</t>
-  </si>
-  <si>
-    <t>orps_denuncia_dictamen_K7_0.05</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_bert_K7_0.05</t>
+    <t>todos_antecedentes_dictamen_K6_0.05</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen_bert</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_dictamen_bert_K6_0.05</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_dictamen_bert_K5_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_K7_0.05</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_bert_K7_0.05</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_dictamen_K7_0.05</t>
   </si>
   <si>
     <t>comisión_lim</t>
   </si>
   <si>
-    <t>comisión_lim_denuncia_dictamen_K3_0.05</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dictamen_bert_K3_0.05</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dictamen_bert_K8_0.05</t>
+    <t>comisión_lim_antecedentes_dictamen_K3_0.05</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dictamen_bert_K3_0.05</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dictamen_bert_K8_0.05</t>
   </si>
   <si>
     <t>contenido_bert</t>
@@ -130,10 +130,10 @@
     <t>comisión_contenido_bert_K10_0.05</t>
   </si>
   <si>
-    <t>orps_denuncia_dictamen_bert_K12_0.01</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dictamen_K15_0.01</t>
+    <t>orps_antecedentes_dictamen_bert_K12_0.01</t>
+  </si>
+  <si>
+    <t>comisión_antecedentes_dictamen_K15_0.01</t>
   </si>
 </sst>
 </file>
@@ -894,10 +894,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
         <v>7</v>
@@ -926,10 +926,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2">
         <v>7</v>
